--- a/results/components/gene_names/p10s4.xlsx
+++ b/results/components/gene_names/p10s4.xlsx
@@ -22,10 +22,10 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Akt1</t>
+    <t>Dif</t>
   </si>
   <si>
-    <t>Rack1</t>
+    <t>Rca1</t>
   </si>
 </sst>
 </file>

--- a/results/components/gene_names/p10s4.xlsx
+++ b/results/components/gene_names/p10s4.xlsx
@@ -22,10 +22,10 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Dif</t>
+    <t>Sxl</t>
   </si>
   <si>
-    <t>Rca1</t>
+    <t>gl</t>
   </si>
 </sst>
 </file>
